--- a/outputs/latest/historical_month_close_forecast_input_template.xlsx
+++ b/outputs/latest/historical_month_close_forecast_input_template.xlsx
@@ -10,7 +10,7 @@
     <sheet name="HistoricalInputTemplate" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HistoricalInputTemplate'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HistoricalInputTemplate'!$A$1:$J$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -495,12 +495,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -515,107 +515,92 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>36.62872053</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>32.30674137</v>
       </c>
       <c r="H2" t="n">
-        <v>33</v>
+        <v>35.35710146</v>
       </c>
       <c r="I2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>과거 월 예시</t>
-        </is>
+        <v>32.625528</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>월마감</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>18.31436027</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>16.15337069</v>
       </c>
       <c r="H3" t="n">
-        <v>38</v>
+        <v>48.27473842</v>
       </c>
       <c r="I3" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>과거 월 예시</t>
-        </is>
+        <v>44.1430225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>목마감</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>3.662872053</v>
       </c>
       <c r="G4" t="n">
-        <v>12.8</v>
+        <v>3.230674137</v>
       </c>
       <c r="H4" t="n">
-        <v>51</v>
+        <v>51.20781463</v>
       </c>
       <c r="I4" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>과거 월 예시</t>
-        </is>
+        <v>46.4353105</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -624,38 +609,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>월초특수</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>3.662872053</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>3.230674137</v>
       </c>
       <c r="H5" t="n">
-        <v>31</v>
+        <v>53.93482072</v>
       </c>
       <c r="I5" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>다음 월은 1부터 다시 시작</t>
-        </is>
+        <v>48.5538625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -664,76 +644,3005 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>목마감</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>50.36449073</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>44.42176939</v>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
+        <v>96.12521846</v>
       </c>
       <c r="I6" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>다음 월은 1부터 다시 시작</t>
-        </is>
+        <v>89.6520055</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3.662872053</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.230674137</v>
+      </c>
+      <c r="H7" t="n">
+        <v>98.30890995</v>
+      </c>
+      <c r="I7" t="n">
+        <v>91.47566550000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>22.89295033</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20.19171336</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>전산침해 이슈</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3.662872053</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.230674137</v>
+      </c>
+      <c r="H9" t="n">
+        <v>111.05429</v>
+      </c>
+      <c r="I9" t="n">
+        <v>103.9079745</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3.662872053</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.230674137</v>
+      </c>
+      <c r="H10" t="n">
+        <v>116.2440164</v>
+      </c>
+      <c r="I10" t="n">
+        <v>108.3732245</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>13.7357702</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.11502802</v>
+      </c>
+      <c r="H11" t="n">
+        <v>126.3565255</v>
+      </c>
+      <c r="I11" t="n">
+        <v>117.3493795</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3.662872053</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.230674137</v>
+      </c>
+      <c r="H12" t="n">
+        <v>130.1937004</v>
+      </c>
+      <c r="I12" t="n">
+        <v>119.8227715</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>15.56720623</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13.73036508</v>
+      </c>
+      <c r="H13" t="n">
+        <v>143.4870656</v>
+      </c>
+      <c r="I13" t="n">
+        <v>131.745276</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3.662872053</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.230674137</v>
+      </c>
+      <c r="H14" t="n">
+        <v>147.0781705</v>
+      </c>
+      <c r="I14" t="n">
+        <v>134.292222</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3.662872053</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.230674137</v>
+      </c>
+      <c r="H15" t="n">
+        <v>150.9460531</v>
+      </c>
+      <c r="I15" t="n">
+        <v>137.58359</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>12.82005219</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11.30735948</v>
+      </c>
+      <c r="H16" t="n">
+        <v>158.639093</v>
+      </c>
+      <c r="I16" t="n">
+        <v>144.967269</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.662872053</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.230674137</v>
+      </c>
+      <c r="H17" t="n">
+        <v>161.8174025</v>
+      </c>
+      <c r="I17" t="n">
+        <v>147.212506</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>15.56720623</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13.73036508</v>
+      </c>
+      <c r="H18" t="n">
+        <v>178.477465</v>
+      </c>
+      <c r="I18" t="n">
+        <v>162.753635</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>3.662872053</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.230674137</v>
+      </c>
+      <c r="H19" t="n">
+        <v>181.5453632</v>
+      </c>
+      <c r="I19" t="n">
+        <v>165.1681985</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>19</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>최종마감</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>10.98861616</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9.692022412</v>
+      </c>
+      <c r="H20" t="n">
+        <v>191.3864614</v>
+      </c>
+      <c r="I20" t="n">
+        <v>174.1015335</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>월초특수</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>59.63890545</v>
+      </c>
+      <c r="G21" t="n">
+        <v>52.23803931</v>
+      </c>
+      <c r="H21" t="n">
+        <v>61.81529944</v>
+      </c>
+      <c r="I21" t="n">
+        <v>56.8260305</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>4.337374942</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.799130132</v>
+      </c>
+      <c r="H22" t="n">
+        <v>68.32915173000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>62.2873355</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>4.337374942</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.799130132</v>
+      </c>
+      <c r="H23" t="n">
+        <v>75.94737411</v>
+      </c>
+      <c r="I23" t="n">
+        <v>68.83212399999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>21.68687471</v>
+      </c>
+      <c r="G24" t="n">
+        <v>18.99565066</v>
+      </c>
+      <c r="H24" t="n">
+        <v>98.17586602999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>88.871172</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>4.337374942</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.799130132</v>
+      </c>
+      <c r="H25" t="n">
+        <v>100.7779276</v>
+      </c>
+      <c r="I25" t="n">
+        <v>90.8832</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>21.68687471</v>
+      </c>
+      <c r="G26" t="n">
+        <v>18.99565066</v>
+      </c>
+      <c r="H26" t="n">
+        <v>116.7798679</v>
+      </c>
+      <c r="I26" t="n">
+        <v>104.7965665</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>4.337374942</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.799130132</v>
+      </c>
+      <c r="H27" t="n">
+        <v>119.276274</v>
+      </c>
+      <c r="I27" t="n">
+        <v>106.6560525</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>4.337374942</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.799130132</v>
+      </c>
+      <c r="H28" t="n">
+        <v>123.1817808</v>
+      </c>
+      <c r="I28" t="n">
+        <v>109.7961005</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>21.68687471</v>
+      </c>
+      <c r="G29" t="n">
+        <v>18.99565066</v>
+      </c>
+      <c r="H29" t="n">
+        <v>132.9395923</v>
+      </c>
+      <c r="I29" t="n">
+        <v>123.2044945</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>4.337374942</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.799130132</v>
+      </c>
+      <c r="H30" t="n">
+        <v>135.6632412</v>
+      </c>
+      <c r="I30" t="n">
+        <v>125.1710525</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>18.4338435</v>
+      </c>
+      <c r="G31" t="n">
+        <v>16.14630306</v>
+      </c>
+      <c r="H31" t="n">
+        <v>152.35106</v>
+      </c>
+      <c r="I31" t="n">
+        <v>134.554109</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>4.337374942</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.799130132</v>
+      </c>
+      <c r="H32" t="n">
+        <v>154.6610245</v>
+      </c>
+      <c r="I32" t="n">
+        <v>136.086807</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>13</v>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>18.4338435</v>
+      </c>
+      <c r="G33" t="n">
+        <v>16.14630306</v>
+      </c>
+      <c r="H33" t="n">
+        <v>167.9922912</v>
+      </c>
+      <c r="I33" t="n">
+        <v>147.69987</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>14</v>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>4.337374942</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.799130132</v>
+      </c>
+      <c r="H34" t="n">
+        <v>170.83918</v>
+      </c>
+      <c r="I34" t="n">
+        <v>149.829626</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>4.337374942</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.799130132</v>
+      </c>
+      <c r="H35" t="n">
+        <v>174.9017047</v>
+      </c>
+      <c r="I35" t="n">
+        <v>153.22189</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16</v>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>최종마감</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>16.26515603</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14.24673799</v>
+      </c>
+      <c r="H36" t="n">
+        <v>186.1020041</v>
+      </c>
+      <c r="I36" t="n">
+        <v>162.877834</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>월초특수</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>31.31578947</v>
+      </c>
+      <c r="G37" t="n">
+        <v>28.36842105</v>
+      </c>
+      <c r="H37" t="n">
+        <v>32.36729846</v>
+      </c>
+      <c r="I37" t="n">
+        <v>29.092543</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3.578947368</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.242105263</v>
+      </c>
+      <c r="H38" t="n">
+        <v>36.4059082</v>
+      </c>
+      <c r="I38" t="n">
+        <v>32.277059</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>12.07894737</v>
+      </c>
+      <c r="G39" t="n">
+        <v>10.94210526</v>
+      </c>
+      <c r="H39" t="n">
+        <v>48.89150534</v>
+      </c>
+      <c r="I39" t="n">
+        <v>43.045085</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3.578947368</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.242105263</v>
+      </c>
+      <c r="H40" t="n">
+        <v>50.96173305</v>
+      </c>
+      <c r="I40" t="n">
+        <v>44.560816</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>13.42105263</v>
+      </c>
+      <c r="G41" t="n">
+        <v>12.15789474</v>
+      </c>
+      <c r="H41" t="n">
+        <v>66.84692195</v>
+      </c>
+      <c r="I41" t="n">
+        <v>58.5709865</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3.578947368</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.242105263</v>
+      </c>
+      <c r="H42" t="n">
+        <v>70.49452279</v>
+      </c>
+      <c r="I42" t="n">
+        <v>61.314292</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3.578947368</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3.242105263</v>
+      </c>
+      <c r="H43" t="n">
+        <v>77.11941766</v>
+      </c>
+      <c r="I43" t="n">
+        <v>66.80291250000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>13.42105263</v>
+      </c>
+      <c r="G44" t="n">
+        <v>12.15789474</v>
+      </c>
+      <c r="H44" t="n">
+        <v>89.69872167</v>
+      </c>
+      <c r="I44" t="n">
+        <v>77.9817345</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>9</v>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>3.578947368</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.242105263</v>
+      </c>
+      <c r="H45" t="n">
+        <v>92.42950811</v>
+      </c>
+      <c r="I45" t="n">
+        <v>80.2711498</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>13.42105263</v>
+      </c>
+      <c r="G46" t="n">
+        <v>12.15789474</v>
+      </c>
+      <c r="H46" t="n">
+        <v>108.176849</v>
+      </c>
+      <c r="I46" t="n">
+        <v>93.3530378</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>11</v>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>3.578947368</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3.242105263</v>
+      </c>
+      <c r="H47" t="n">
+        <v>110.7251389</v>
+      </c>
+      <c r="I47" t="n">
+        <v>95.19623780000001</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>12</v>
+      </c>
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>3.578947368</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3.242105263</v>
+      </c>
+      <c r="H48" t="n">
+        <v>114.0482917</v>
+      </c>
+      <c r="I48" t="n">
+        <v>97.8443158</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>13</v>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>11.63157895</v>
+      </c>
+      <c r="G49" t="n">
+        <v>10.53684211</v>
+      </c>
+      <c r="H49" t="n">
+        <v>125.8903205</v>
+      </c>
+      <c r="I49" t="n">
+        <v>108.5938278</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2.684210526</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.431578947</v>
+      </c>
+      <c r="H50" t="n">
+        <v>129.2013379</v>
+      </c>
+      <c r="I50" t="n">
+        <v>110.7162918</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>15</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>13.42105263</v>
+      </c>
+      <c r="G51" t="n">
+        <v>12.15789474</v>
+      </c>
+      <c r="H51" t="n">
+        <v>142.7498295</v>
+      </c>
+      <c r="I51" t="n">
+        <v>122.4310753</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16</v>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>3.578947368</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3.242105263</v>
+      </c>
+      <c r="H52" t="n">
+        <v>145.4019072</v>
+      </c>
+      <c r="I52" t="n">
+        <v>124.4832393</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>17</v>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>3.578947368</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.242105263</v>
+      </c>
+      <c r="H53" t="n">
+        <v>147.865743</v>
+      </c>
+      <c r="I53" t="n">
+        <v>126.3340983</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>18</v>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>11.63157895</v>
+      </c>
+      <c r="G54" t="n">
+        <v>10.53684211</v>
+      </c>
+      <c r="H54" t="n">
+        <v>157.963969</v>
+      </c>
+      <c r="I54" t="n">
+        <v>135.1480423</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>19</v>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2.684210526</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.431578947</v>
+      </c>
+      <c r="H55" t="n">
+        <v>159.523989</v>
+      </c>
+      <c r="I55" t="n">
+        <v>136.4484173</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>20</v>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>최종마감</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>12.07894737</v>
+      </c>
+      <c r="G56" t="n">
+        <v>10.94210526</v>
+      </c>
+      <c r="H56" t="n">
+        <v>171.2023836</v>
+      </c>
+      <c r="I56" t="n">
+        <v>146.9859523</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>월초특수</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>31.41045286</v>
+      </c>
+      <c r="G57" t="n">
+        <v>28.29343456</v>
+      </c>
+      <c r="H57" t="n">
+        <v>31.22132807</v>
+      </c>
+      <c r="I57" t="n">
+        <v>28.3685645</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2.692324531</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.425151534</v>
+      </c>
+      <c r="H58" t="n">
+        <v>34.07434335</v>
+      </c>
+      <c r="I58" t="n">
+        <v>30.5018315</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C59" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>월마감</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>47</v>
-      </c>
-      <c r="I7" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>다음 월은 1부터 다시 시작</t>
-        </is>
+      <c r="F59" t="n">
+        <v>17.9488302</v>
+      </c>
+      <c r="G59" t="n">
+        <v>16.16767689</v>
+      </c>
+      <c r="H59" t="n">
+        <v>48.30695044</v>
+      </c>
+      <c r="I59" t="n">
+        <v>42.8446345</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>3.589766041</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.233535378</v>
+      </c>
+      <c r="H60" t="n">
+        <v>50.8733258</v>
+      </c>
+      <c r="I60" t="n">
+        <v>44.7965565</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>3.589766041</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3.233535378</v>
+      </c>
+      <c r="H61" t="n">
+        <v>54.09075513</v>
+      </c>
+      <c r="I61" t="n">
+        <v>47.3514275</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>15.25650567</v>
+      </c>
+      <c r="G62" t="n">
+        <v>13.74252536</v>
+      </c>
+      <c r="H62" t="n">
+        <v>64.23360108</v>
+      </c>
+      <c r="I62" t="n">
+        <v>56.2895675</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>7</v>
+      </c>
+      <c r="D63" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>3.589766041</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3.233535378</v>
+      </c>
+      <c r="H63" t="n">
+        <v>66.37076295</v>
+      </c>
+      <c r="I63" t="n">
+        <v>58.0229495</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>17.9488302</v>
+      </c>
+      <c r="G64" t="n">
+        <v>16.16767689</v>
+      </c>
+      <c r="H64" t="n">
+        <v>79.14527067</v>
+      </c>
+      <c r="I64" t="n">
+        <v>69.19543349999999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>9</v>
+      </c>
+      <c r="D65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>3.589766041</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3.233535378</v>
+      </c>
+      <c r="H65" t="n">
+        <v>80.96060982</v>
+      </c>
+      <c r="I65" t="n">
+        <v>70.5479735</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>10</v>
+      </c>
+      <c r="D66" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>3.589766041</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3.233535378</v>
+      </c>
+      <c r="H66" t="n">
+        <v>83.82798072</v>
+      </c>
+      <c r="I66" t="n">
+        <v>72.186857</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>11</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>15.25650567</v>
+      </c>
+      <c r="G67" t="n">
+        <v>13.74252536</v>
+      </c>
+      <c r="H67" t="n">
+        <v>94.68462341</v>
+      </c>
+      <c r="I67" t="n">
+        <v>81.10643399999999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>12</v>
+      </c>
+      <c r="D68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2.692324531</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2.425151534</v>
+      </c>
+      <c r="H68" t="n">
+        <v>96.1271375</v>
+      </c>
+      <c r="I68" t="n">
+        <v>82.22879450000001</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>13</v>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>22.43603776</v>
+      </c>
+      <c r="G69" t="n">
+        <v>20.20959611</v>
+      </c>
+      <c r="H69" t="n">
+        <v>113.2358376</v>
+      </c>
+      <c r="I69" t="n">
+        <v>97.4365605</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>14</v>
+      </c>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>3.589766041</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3.233535378</v>
+      </c>
+      <c r="H70" t="n">
+        <v>116.1692259</v>
+      </c>
+      <c r="I70" t="n">
+        <v>99.2379205</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>15</v>
+      </c>
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>3.589766041</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3.233535378</v>
+      </c>
+      <c r="H71" t="n">
+        <v>118.6223869</v>
+      </c>
+      <c r="I71" t="n">
+        <v>101.1183365</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16</v>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>10.76929812</v>
+      </c>
+      <c r="G72" t="n">
+        <v>9.700606134999999</v>
+      </c>
+      <c r="H72" t="n">
+        <v>126.8726695</v>
+      </c>
+      <c r="I72" t="n">
+        <v>108.3754935</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>17</v>
+      </c>
+      <c r="D73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>2.692324531</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2.425151534</v>
+      </c>
+      <c r="H73" t="n">
+        <v>128.880539</v>
+      </c>
+      <c r="I73" t="n">
+        <v>109.9560555</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>20</v>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>최종마감</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>10.76929812</v>
+      </c>
+      <c r="G74" t="n">
+        <v>9.700606134999999</v>
+      </c>
+      <c r="H74" t="n">
+        <v>141.404429</v>
+      </c>
+      <c r="I74" t="n">
+        <v>121.0004095</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>월초특수</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>39.86830729</v>
+      </c>
+      <c r="G75" t="n">
+        <v>36.28631325</v>
+      </c>
+      <c r="H75" t="n">
+        <v>36.48991063</v>
+      </c>
+      <c r="I75" t="n">
+        <v>32.912721</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>4.429811921</v>
+      </c>
+      <c r="G76" t="n">
+        <v>4.031812583</v>
+      </c>
+      <c r="H76" t="n">
+        <v>41.56605968</v>
+      </c>
+      <c r="I76" t="n">
+        <v>37.0279795</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>17.71924768</v>
+      </c>
+      <c r="G77" t="n">
+        <v>16.12725033</v>
+      </c>
+      <c r="H77" t="n">
+        <v>55.43600333</v>
+      </c>
+      <c r="I77" t="n">
+        <v>49.7902305</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>4</v>
+      </c>
+      <c r="D78" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>2.657887152</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2.41908755</v>
+      </c>
+      <c r="H78" t="n">
+        <v>58.45108318</v>
+      </c>
+      <c r="I78" t="n">
+        <v>52.274435</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>5</v>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>15.06136053</v>
+      </c>
+      <c r="G79" t="n">
+        <v>13.70816278</v>
+      </c>
+      <c r="H79" t="n">
+        <v>74.26344671</v>
+      </c>
+      <c r="I79" t="n">
+        <v>66.292158</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>6</v>
+      </c>
+      <c r="D80" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>2.657887152</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2.41908755</v>
+      </c>
+      <c r="H80" t="n">
+        <v>76.67756548</v>
+      </c>
+      <c r="I80" t="n">
+        <v>68.16397000000001</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>7</v>
+      </c>
+      <c r="D81" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>2.657887152</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2.41908755</v>
+      </c>
+      <c r="H81" t="n">
+        <v>79.53337121</v>
+      </c>
+      <c r="I81" t="n">
+        <v>70.615582</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>8</v>
+      </c>
+      <c r="D82" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>11.51751099</v>
+      </c>
+      <c r="G82" t="n">
+        <v>10.48271272</v>
+      </c>
+      <c r="H82" t="n">
+        <v>89.3880966</v>
+      </c>
+      <c r="I82" t="n">
+        <v>79.19153799999999</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>9</v>
+      </c>
+      <c r="D83" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>2.657887152</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2.41908755</v>
+      </c>
+      <c r="H83" t="n">
+        <v>91.24684874</v>
+      </c>
+      <c r="I83" t="n">
+        <v>80.77955</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>10</v>
+      </c>
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>13.28943576</v>
+      </c>
+      <c r="G84" t="n">
+        <v>12.09543775</v>
+      </c>
+      <c r="H84" t="n">
+        <v>102.087537</v>
+      </c>
+      <c r="I84" t="n">
+        <v>89.61383650000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>11</v>
+      </c>
+      <c r="D85" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>2.657887152</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2.41908755</v>
+      </c>
+      <c r="H85" t="n">
+        <v>104.1906677</v>
+      </c>
+      <c r="I85" t="n">
+        <v>91.2505225</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>12</v>
+      </c>
+      <c r="D86" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>2.657887152</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2.41908755</v>
+      </c>
+      <c r="H86" t="n">
+        <v>106.1251762</v>
+      </c>
+      <c r="I86" t="n">
+        <v>92.75183850000001</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>13</v>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>목마감</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>11.51751099</v>
+      </c>
+      <c r="G87" t="n">
+        <v>10.48271272</v>
+      </c>
+      <c r="H87" t="n">
+        <v>113.7797958</v>
+      </c>
+      <c r="I87" t="n">
+        <v>99.3235875</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>14</v>
+      </c>
+      <c r="D88" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>2.657887152</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2.41908755</v>
+      </c>
+      <c r="H88" t="n">
+        <v>117.5584498</v>
+      </c>
+      <c r="I88" t="n">
+        <v>102.4638375</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>15</v>
+      </c>
+      <c r="D89" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>월마감</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>11.51751099</v>
+      </c>
+      <c r="G89" t="n">
+        <v>10.48271272</v>
+      </c>
+      <c r="H89" t="n">
+        <v>129.3673789</v>
+      </c>
+      <c r="I89" t="n">
+        <v>112.691359</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>16</v>
+      </c>
+      <c r="D90" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>2.657887152</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2.41908755</v>
+      </c>
+      <c r="H90" t="n">
+        <v>131.2191114</v>
+      </c>
+      <c r="I90" t="n">
+        <v>114.1061695</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>17</v>
+      </c>
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>최종마감</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>8.859623840999999</v>
+      </c>
+      <c r="G91" t="n">
+        <v>8.063625167</v>
+      </c>
+      <c r="H91" t="n">
+        <v>139.2401079</v>
+      </c>
+      <c r="I91" t="n">
+        <v>121.1395195</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J7"/>
+  <autoFilter ref="A1:J91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>